--- a/Price and products last2.xlsx
+++ b/Price and products last2.xlsx
@@ -1,27 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshitmittal/Desktop/product_pricing_app/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B832D-3055-FA4A-9764-53B9E73778E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Chain Pulley Block" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Monorail Travelling Trolley" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Winch Machine" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Electric Winch Machine" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Electric Chain Hoist" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="Electric Wire Rope Hoist" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="Portable Gantry Crane" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="Shearleg Tripod" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="Hydraulic Pallet Truck" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="Hydraulic Hand Stacker" sheetId="10" r:id="rId13"/>
-    <sheet state="visible" name="Hydraulic Scissor Table" sheetId="11" r:id="rId14"/>
+    <sheet name="Chain Pulley Block" sheetId="1" r:id="rId1"/>
+    <sheet name="Monorail Travelling Trolley" sheetId="2" r:id="rId2"/>
+    <sheet name="Winch Machine" sheetId="3" r:id="rId3"/>
+    <sheet name="Electric Winch Machine" sheetId="4" r:id="rId4"/>
+    <sheet name="Electric Chain Hoist" sheetId="5" r:id="rId5"/>
+    <sheet name="Electric Wire Rope Hoist" sheetId="6" r:id="rId6"/>
+    <sheet name="Portable Gantry Crane" sheetId="7" r:id="rId7"/>
+    <sheet name="Shearleg Tripod" sheetId="8" r:id="rId8"/>
+    <sheet name="Hydraulic Pallet Truck" sheetId="9" r:id="rId9"/>
+    <sheet name="Hydraulic Scissor Table" sheetId="11" r:id="rId10"/>
+    <sheet name="Hydraulic Mobile Floor Crane" sheetId="12" r:id="rId11"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="200">
   <si>
     <t>Product Name</t>
   </si>
@@ -587,69 +596,97 @@
     <t>HPT2.5B</t>
   </si>
   <si>
-    <t>HPT4</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Hydraulic Hand Stacker</t>
-  </si>
-  <si>
-    <t>Hand Stacker</t>
-  </si>
-  <si>
-    <t>HHS1</t>
-  </si>
-  <si>
-    <t>HHS2</t>
-  </si>
-  <si>
     <t>Hydraulic Scissor Table</t>
   </si>
   <si>
-    <t>Scissor Table</t>
-  </si>
-  <si>
     <t>HST1</t>
   </si>
   <si>
     <t>HST1.5</t>
+  </si>
+  <si>
+    <t>Single Scissor</t>
+  </si>
+  <si>
+    <t>Double Scissor</t>
+  </si>
+  <si>
+    <t>HDS1</t>
+  </si>
+  <si>
+    <t>HDS1.5</t>
+  </si>
+  <si>
+    <t>Range(in Ton)</t>
+  </si>
+  <si>
+    <t>Hydraulic Mobile Floor Crane</t>
+  </si>
+  <si>
+    <t>with Nylon Wheel</t>
+  </si>
+  <si>
+    <t>HJC1</t>
+  </si>
+  <si>
+    <t>HJC2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -663,6 +700,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -674,6 +712,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -682,6 +722,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -690,30 +733,38 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -723,137 +774,133 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1043,25 +1090,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.5"/>
-    <col customWidth="1" min="2" max="2" width="19.38"/>
-    <col customWidth="1" min="3" max="3" width="5.88"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.25"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,175 +1131,175 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>6176.0</v>
+        <v>6176</v>
       </c>
       <c r="F2" s="2">
-        <v>395.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>8118.0</v>
+        <v>8118</v>
       </c>
       <c r="F3" s="2">
-        <v>460.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>10487.0</v>
+        <v>10487</v>
       </c>
       <c r="F4" s="2">
-        <v>710.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>12059.0</v>
+        <v>12059</v>
       </c>
       <c r="F5" s="2">
-        <v>800.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>15691.0</v>
+        <v>15691</v>
       </c>
       <c r="F6" s="2">
-        <v>1000.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1">
-        <v>24932.0</v>
+        <v>24932</v>
       </c>
       <c r="F7" s="2">
-        <v>1820.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>8832.0</v>
+        <v>8832</v>
       </c>
       <c r="F8" s="2">
-        <v>553.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>9953.0</v>
+        <v>9953</v>
       </c>
       <c r="F9" s="2">
-        <v>553.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>11690.0</v>
+        <v>11690</v>
       </c>
       <c r="F10" s="2">
-        <v>820.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+        <v>820</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>18913.0</v>
+        <v>18913</v>
       </c>
       <c r="F11" s="2">
-        <v>1145.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1257,161 +1307,161 @@
         <v>7.5</v>
       </c>
       <c r="E12" s="1">
-        <v>24074.0</v>
+        <v>24074</v>
       </c>
       <c r="F12" s="2">
-        <v>1600.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1">
-        <v>32413.0</v>
+        <v>32413</v>
       </c>
       <c r="F13" s="2">
-        <v>2015.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1">
-        <v>93584.0</v>
+        <v>93584</v>
       </c>
       <c r="F14" s="2">
-        <v>3338.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1">
-        <v>143319.0</v>
+        <v>143319</v>
       </c>
       <c r="F15" s="2">
-        <v>4167.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1">
-        <v>186791.0</v>
+        <v>186791</v>
       </c>
       <c r="F16" s="2">
-        <v>5000.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1">
-        <v>384300.0</v>
+        <v>384300</v>
       </c>
       <c r="F17" s="2">
-        <v>6200.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="3" t="s">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>28355.0</v>
+        <v>28355</v>
       </c>
       <c r="F18" s="2">
-        <v>676.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>32030.0</v>
+        <v>32030</v>
       </c>
       <c r="F19" s="2">
-        <v>676.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1">
-        <v>38710.0</v>
+        <v>38710</v>
       </c>
       <c r="F20" s="2">
-        <v>1016.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>59632.0</v>
+        <v>59632</v>
       </c>
       <c r="F21" s="2">
-        <v>1430.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1419,76 +1469,76 @@
         <v>7.5</v>
       </c>
       <c r="E22" s="1">
-        <v>84862.0</v>
+        <v>84862</v>
       </c>
       <c r="F22" s="2">
-        <v>1998.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1">
-        <v>104358.0</v>
+        <v>104358</v>
       </c>
       <c r="F23" s="2">
-        <v>2540.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="10"/>
+      <c r="B24" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>9960.0</v>
+        <v>9960</v>
       </c>
       <c r="F24" s="2">
-        <v>590.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>12500.0</v>
+        <v>12500</v>
       </c>
       <c r="F25" s="2">
-        <v>870.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+        <v>870</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E26" s="1">
-        <v>16700.0</v>
+        <v>16700</v>
       </c>
       <c r="F26" s="2">
-        <v>1200.0</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -1499,28 +1549,29 @@
     <mergeCell ref="B18:B23"/>
     <mergeCell ref="B24:B26"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0000FF"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.13"/>
-    <col customWidth="1" min="2" max="2" width="10.75"/>
-    <col customWidth="1" min="3" max="3" width="5.88"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.25"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="17" t="s">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -1534,35 +1585,139 @@
       <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="18" t="s">
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="17">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17">
+        <v>61875</v>
+      </c>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="16"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="D3" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="17">
+        <v>67500</v>
+      </c>
+      <c r="F3" s="19"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="16"/>
+      <c r="B4" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="17">
-        <v>84000.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="17" t="s">
+      <c r="C4" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="17">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="17">
-        <v>98750.0</v>
+      <c r="D4" s="24">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24">
+        <v>64375</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="23">
+        <v>70000</v>
+      </c>
+      <c r="F5" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B4:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96417A8F-B8C7-D64F-AE67-B97D41C137A4}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="24">
+        <v>1</v>
+      </c>
+      <c r="E2" s="24">
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="24">
+        <v>2</v>
+      </c>
+      <c r="E3" s="24">
+        <v>59250</v>
       </c>
     </row>
   </sheetData>
@@ -1570,97 +1725,27 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0000FF"/>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="17.75"/>
-    <col customWidth="1" min="2" max="2" width="10.38"/>
-    <col customWidth="1" min="3" max="3" width="6.13"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.25"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="1">
-        <v>68000.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E3" s="1">
-        <v>76000.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-  </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.63"/>
-    <col customWidth="1" min="2" max="2" width="14.88"/>
-    <col customWidth="1" min="3" max="3" width="5.88"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.25"/>
-    <col customWidth="1" min="6" max="6" width="16.75"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1680,261 +1765,261 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>5201.0</v>
+        <v>5201</v>
       </c>
       <c r="F2" s="2">
-        <v>205.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>6462.0</v>
+        <v>6462</v>
       </c>
       <c r="F3" s="2">
-        <v>205.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>9026.0</v>
+        <v>9026</v>
       </c>
       <c r="F4" s="2">
-        <v>205.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>11349.0</v>
+        <v>11349</v>
       </c>
       <c r="F5" s="2">
-        <v>205.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1">
-        <v>24721.0</v>
+        <v>24721</v>
       </c>
       <c r="F6" s="2">
-        <v>205.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>43429.0</v>
+        <v>43429</v>
       </c>
       <c r="F7" s="2">
-        <v>320.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>65206.0</v>
+        <v>65206</v>
       </c>
       <c r="F8" s="2">
-        <v>320.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>20615.0</v>
+        <v>20615</v>
       </c>
       <c r="F9" s="2">
-        <v>235.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1">
-        <v>25445.0</v>
+        <v>25445</v>
       </c>
       <c r="F10" s="2">
-        <v>235.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="1">
-        <v>32738.0</v>
+        <v>32738</v>
       </c>
       <c r="F11" s="2">
-        <v>235.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>43603.0</v>
+        <v>43603</v>
       </c>
       <c r="F12" s="2">
-        <v>235.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1">
-        <v>95662.0</v>
+        <v>95662</v>
       </c>
       <c r="F13" s="2">
-        <v>235.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10"/>
+      <c r="B14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>4941.0</v>
-      </c>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+        <v>4941</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>6139.0</v>
-      </c>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+        <v>6139</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="1">
-        <v>8575.0</v>
-      </c>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
+        <v>8575</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>10782.0</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>10782</v>
+      </c>
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1943,24 +2028,25 @@
     <mergeCell ref="B9:B13"/>
     <mergeCell ref="B14:B17"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="2" width="21.63"/>
-    <col customWidth="1" min="3" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.75"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1977,11 +2063,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1991,25 +2077,25 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="1">
-        <v>4560.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>5440.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
+        <v>5440</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,100 +2103,100 @@
         <v>1.5</v>
       </c>
       <c r="E4" s="1">
-        <v>6400.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3" t="s">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>23195.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>23195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>30965.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+        <v>30965</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D7" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>52920.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+        <v>52920</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>99900.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+        <v>99900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1">
-        <v>184095.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>184095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>279940.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+        <v>279940</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1">
-        <v>320500.0</v>
+        <v>320500</v>
       </c>
     </row>
   </sheetData>
@@ -2119,21 +2205,22 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="9" max="9" width="23.75"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2162,93 +2249,93 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G2" s="1">
-        <v>134765.0</v>
+        <v>134765</v>
       </c>
       <c r="H2" s="2">
-        <v>27225.0</v>
+        <v>27225</v>
       </c>
       <c r="I2" s="2">
-        <v>63885.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>63885</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G3" s="1">
-        <v>140845.0</v>
+        <v>140845</v>
       </c>
       <c r="H3" s="2">
-        <v>34255.0</v>
+        <v>34255</v>
       </c>
       <c r="I3" s="2">
-        <v>63885.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>63885</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>171230.0</v>
+        <v>171230</v>
       </c>
       <c r="H4" s="2">
-        <v>34255.0</v>
+        <v>34255</v>
       </c>
       <c r="I4" s="2">
-        <v>63885.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>63885</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D5" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>7.5</v>
@@ -2257,23 +2344,23 @@
         <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>265140.0</v>
+        <v>265140</v>
       </c>
       <c r="H5" s="2">
-        <v>40305.0</v>
+        <v>40305</v>
       </c>
       <c r="I5" s="2">
-        <v>63885.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>63885</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <v>5.2</v>
@@ -2282,23 +2369,23 @@
         <v>57</v>
       </c>
       <c r="G6" s="1">
-        <v>208890.0</v>
+        <v>208890</v>
       </c>
       <c r="H6" s="2">
-        <v>40305.0</v>
+        <v>40305</v>
       </c>
       <c r="I6" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
         <v>5.2</v>
@@ -2307,23 +2394,23 @@
         <v>64</v>
       </c>
       <c r="G7" s="1">
-        <v>242545.0</v>
+        <v>242545</v>
       </c>
       <c r="H7" s="2">
-        <v>40305.0</v>
+        <v>40305</v>
       </c>
       <c r="I7" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
         <v>7.5</v>
@@ -2332,23 +2419,23 @@
         <v>57</v>
       </c>
       <c r="G8" s="1">
-        <v>223645.0</v>
+        <v>223645</v>
       </c>
       <c r="H8" s="2">
-        <v>50565.0</v>
+        <v>50565</v>
       </c>
       <c r="I8" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
         <v>7.5</v>
@@ -2357,23 +2444,23 @@
         <v>64</v>
       </c>
       <c r="G9" s="1">
-        <v>230600.0</v>
+        <v>230600</v>
       </c>
       <c r="H9" s="2">
-        <v>50565.0</v>
+        <v>50565</v>
       </c>
       <c r="I9" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1">
         <v>6.5</v>
@@ -2382,23 +2469,23 @@
         <v>68</v>
       </c>
       <c r="G10" s="1">
-        <v>314685.0</v>
+        <v>314685</v>
       </c>
       <c r="H10" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I10" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1">
         <v>6.5</v>
@@ -2407,23 +2494,23 @@
         <v>70</v>
       </c>
       <c r="G11" s="1">
-        <v>327000.0</v>
+        <v>327000</v>
       </c>
       <c r="H11" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I11" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
         <v>6.5</v>
@@ -2432,23 +2519,23 @@
         <v>72</v>
       </c>
       <c r="G12" s="1">
-        <v>398555.0</v>
+        <v>398555</v>
       </c>
       <c r="H12" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I12" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D13" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
         <v>6.5</v>
@@ -2457,118 +2544,118 @@
         <v>74</v>
       </c>
       <c r="G13" s="1">
-        <v>408585.0</v>
+        <v>408585</v>
       </c>
       <c r="H13" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I13" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G14" s="1">
-        <v>369355.0</v>
+        <v>369355</v>
       </c>
       <c r="H14" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I14" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G15" s="1">
-        <v>382000.0</v>
+        <v>382000</v>
       </c>
       <c r="H15" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I15" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D16" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G16" s="1">
-        <v>416615.0</v>
+        <v>416615</v>
       </c>
       <c r="H16" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I16" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D17" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G17" s="1">
-        <v>462555.0</v>
+        <v>462555</v>
       </c>
       <c r="H17" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I17" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
@@ -2576,24 +2663,24 @@
         <v>7.5</v>
       </c>
       <c r="E18" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G18" s="1">
-        <v>495620.0</v>
+        <v>495620</v>
       </c>
       <c r="H18" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I18" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
@@ -2601,24 +2688,24 @@
         <v>7.5</v>
       </c>
       <c r="E19" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G19" s="1">
-        <v>503845.0</v>
+        <v>503845</v>
       </c>
       <c r="H19" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I19" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
@@ -2626,24 +2713,24 @@
         <v>7.5</v>
       </c>
       <c r="E20" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G20" s="1">
-        <v>526035.0</v>
+        <v>526035</v>
       </c>
       <c r="H20" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I20" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2651,24 +2738,24 @@
         <v>7.5</v>
       </c>
       <c r="E21" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G21" s="1">
-        <v>556620.0</v>
+        <v>556620</v>
       </c>
       <c r="H21" s="2">
-        <v>53445.0</v>
+        <v>53445</v>
       </c>
       <c r="I21" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="3" t="s">
         <v>83</v>
       </c>
@@ -2682,18 +2769,18 @@
         <v>57</v>
       </c>
       <c r="G22" s="1">
-        <v>529295.0</v>
+        <v>529295</v>
       </c>
       <c r="H22" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I22" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="3" t="s">
         <v>84</v>
       </c>
@@ -2707,18 +2794,18 @@
         <v>64</v>
       </c>
       <c r="G23" s="1">
-        <v>535530.0</v>
+        <v>535530</v>
       </c>
       <c r="H23" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I23" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="3" t="s">
         <v>85</v>
       </c>
@@ -2732,18 +2819,18 @@
         <v>72</v>
       </c>
       <c r="G24" s="1">
-        <v>559820.0</v>
+        <v>559820</v>
       </c>
       <c r="H24" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I24" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="3" t="s">
         <v>86</v>
       </c>
@@ -2757,23 +2844,23 @@
         <v>74</v>
       </c>
       <c r="G25" s="1">
-        <v>588070.0</v>
+        <v>588070</v>
       </c>
       <c r="H25" s="2">
-        <v>70165.0</v>
+        <v>70165</v>
       </c>
       <c r="I25" s="2">
-        <v>66665.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+        <v>66665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1">
         <v>4.8</v>
@@ -2782,23 +2869,23 @@
         <v>57</v>
       </c>
       <c r="G26" s="1">
-        <v>587685.0</v>
+        <v>587685</v>
       </c>
       <c r="H26" s="2">
-        <v>76225.0</v>
+        <v>76225</v>
       </c>
       <c r="I26" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D27" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1">
         <v>4.8</v>
@@ -2807,23 +2894,23 @@
         <v>64</v>
       </c>
       <c r="G27" s="1">
-        <v>605830.0</v>
+        <v>605830</v>
       </c>
       <c r="H27" s="2">
-        <v>76225.0</v>
+        <v>76225</v>
       </c>
       <c r="I27" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D28" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1">
         <v>4.8</v>
@@ -2832,23 +2919,23 @@
         <v>72</v>
       </c>
       <c r="G28" s="1">
-        <v>687835.0</v>
+        <v>687835</v>
       </c>
       <c r="H28" s="2">
-        <v>76225.0</v>
+        <v>76225</v>
       </c>
       <c r="I28" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D29" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1">
         <v>4.8</v>
@@ -2857,23 +2944,23 @@
         <v>74</v>
       </c>
       <c r="G29" s="1">
-        <v>709300.0</v>
+        <v>709300</v>
       </c>
       <c r="H29" s="2">
-        <v>76225.0</v>
+        <v>76225</v>
       </c>
       <c r="I29" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D30" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1">
         <v>4.5</v>
@@ -2882,23 +2969,23 @@
         <v>57</v>
       </c>
       <c r="G30" s="1">
-        <v>798270.0</v>
+        <v>798270</v>
       </c>
       <c r="H30" s="2">
-        <v>86595.0</v>
+        <v>86595</v>
       </c>
       <c r="I30" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D31" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1">
         <v>4.5</v>
@@ -2907,23 +2994,23 @@
         <v>64</v>
       </c>
       <c r="G31" s="1">
-        <v>821220.0</v>
+        <v>821220</v>
       </c>
       <c r="H31" s="2">
-        <v>86595.0</v>
+        <v>86595</v>
       </c>
       <c r="I31" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D32" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1">
         <v>4.5</v>
@@ -2932,23 +3019,23 @@
         <v>72</v>
       </c>
       <c r="G32" s="1">
-        <v>1006195.0</v>
+        <v>1006195</v>
       </c>
       <c r="H32" s="2">
-        <v>86595.0</v>
+        <v>86595</v>
       </c>
       <c r="I32" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D33" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1">
         <v>4.5</v>
@@ -2957,63 +3044,63 @@
         <v>74</v>
       </c>
       <c r="G33" s="1">
-        <v>1035645.0</v>
+        <v>1035645</v>
       </c>
       <c r="H33" s="2">
-        <v>86595.0</v>
+        <v>86595</v>
       </c>
       <c r="I33" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D34" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>96</v>
       </c>
       <c r="G34" s="1">
-        <v>1296285.0</v>
+        <v>1296285</v>
       </c>
       <c r="H34" s="2">
-        <v>105555.0</v>
+        <v>105555</v>
       </c>
       <c r="I34" s="2">
-        <v>72225.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
+        <v>72225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D35" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>98</v>
       </c>
       <c r="G35" s="1">
-        <v>1427170.0</v>
+        <v>1427170</v>
       </c>
       <c r="H35" s="2">
-        <v>105555.0</v>
+        <v>105555</v>
       </c>
       <c r="I35" s="2">
-        <v>72225.0</v>
+        <v>72225</v>
       </c>
     </row>
   </sheetData>
@@ -3021,63 +3108,64 @@
     <mergeCell ref="A2:A35"/>
     <mergeCell ref="B2:B35"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.63"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="12.13"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="8.63"/>
-    <col customWidth="1" min="6" max="6" width="10.25"/>
-    <col customWidth="1" min="7" max="7" width="17.0"/>
-    <col customWidth="1" min="8" max="8" width="15.88"/>
-    <col customWidth="1" min="9" max="14" width="18.0"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3096,217 +3184,218 @@
       <c r="K2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>66665.0</v>
+        <v>66665</v>
       </c>
       <c r="G3" s="1">
-        <v>410.0</v>
+        <v>410</v>
       </c>
       <c r="H3" s="1">
-        <v>71865.0</v>
+        <v>71865</v>
       </c>
       <c r="I3" s="1">
-        <v>565.0</v>
+        <v>565</v>
       </c>
       <c r="J3" s="1">
-        <v>101545.0</v>
+        <v>101545</v>
       </c>
       <c r="K3" s="1">
-        <v>410.0</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1" t="s">
         <v>107</v>
       </c>
       <c r="D4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>70000.0</v>
+        <v>70000</v>
       </c>
       <c r="G4" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="H4" s="1">
-        <v>76450.0</v>
+        <v>76450</v>
       </c>
       <c r="I4" s="1">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="J4" s="1">
-        <v>104875.0</v>
+        <v>104875</v>
       </c>
       <c r="K4" s="1">
-        <v>785.0</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>785</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>82270.0</v>
+        <v>82270</v>
       </c>
       <c r="G5" s="1">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="1">
-        <v>91300.0</v>
+        <v>91300</v>
       </c>
       <c r="I5" s="1">
-        <v>1155.0</v>
+        <v>1155</v>
       </c>
       <c r="J5" s="1">
-        <v>116265.0</v>
+        <v>116265</v>
       </c>
       <c r="K5" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>97155.0</v>
+        <v>97155</v>
       </c>
       <c r="G6" s="1">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="1">
-        <v>108500.0</v>
+        <v>108500</v>
       </c>
       <c r="I6" s="1">
-        <v>1155.0</v>
+        <v>1155</v>
       </c>
       <c r="J6" s="1">
-        <v>140000.0</v>
+        <v>140000</v>
       </c>
       <c r="K6" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
+        <v>1000</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="5" max="5" width="8.63"/>
-    <col customWidth="1" min="6" max="6" width="10.25"/>
-    <col customWidth="1" min="7" max="7" width="17.0"/>
-    <col customWidth="1" min="8" max="8" width="18.0"/>
-    <col customWidth="1" min="9" max="9" width="17.0"/>
-    <col customWidth="1" min="11" max="11" width="13.5"/>
-    <col customWidth="1" min="13" max="14" width="15.63"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="13" max="14" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="10"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="15"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3335,11 +3424,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3349,741 +3438,741 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1">
-        <v>61500.0</v>
-      </c>
-      <c r="G3" s="13"/>
+        <v>61500</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1">
-        <v>88000.0</v>
-      </c>
-      <c r="I3" s="13"/>
+        <v>88000</v>
+      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K3" s="2">
-        <v>49950.0</v>
-      </c>
-      <c r="L3" s="6"/>
+        <v>49950</v>
+      </c>
+      <c r="L3" s="2"/>
       <c r="M3" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N3" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1">
-        <v>85000.0</v>
+        <v>85000</v>
       </c>
       <c r="G4" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="H4" s="1">
-        <v>118530.0</v>
+        <v>118530</v>
       </c>
       <c r="I4" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="J4" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K4" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L4" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M4" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N4" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1">
-        <v>106075.0</v>
+        <v>106075</v>
       </c>
       <c r="G5" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="H5" s="1">
-        <v>142115.0</v>
+        <v>142115</v>
       </c>
       <c r="I5" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="J5" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K5" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L5" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M5" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N5" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>111900.0</v>
+        <v>111900</v>
       </c>
       <c r="G6" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="H6" s="1">
-        <v>147950.0</v>
+        <v>147950</v>
       </c>
       <c r="I6" s="1">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="J6" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K6" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L6" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M6" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N6" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D7" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1">
-        <v>95516.0</v>
-      </c>
-      <c r="G7" s="13"/>
+        <v>95516</v>
+      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
-        <v>130563.0</v>
-      </c>
-      <c r="I7" s="13"/>
+        <v>130563</v>
+      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K7" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L7" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M7" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N7" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1">
-        <v>116500.0</v>
-      </c>
-      <c r="G8" s="13"/>
+        <v>116500</v>
+      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1">
-        <v>154000.0</v>
-      </c>
-      <c r="I8" s="13"/>
+        <v>154000</v>
+      </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K8" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L8" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M8" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N8" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="13"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="2">
-        <v>31580.0</v>
+        <v>31580</v>
       </c>
       <c r="K9" s="2">
-        <v>49950.0</v>
+        <v>49950</v>
       </c>
       <c r="L9" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M9" s="2">
-        <v>7600.0</v>
+        <v>7600</v>
       </c>
       <c r="N9" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1">
-        <v>125600.0</v>
+        <v>125600</v>
       </c>
       <c r="G10" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="H10" s="1">
-        <v>171160.0</v>
+        <v>171160</v>
       </c>
       <c r="I10" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="J10" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K10" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L10" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M10" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N10" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D11" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1">
-        <v>148000.0</v>
+        <v>148000</v>
       </c>
       <c r="G11" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="H11" s="1">
-        <v>204160.0</v>
+        <v>204160</v>
       </c>
       <c r="I11" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="J11" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K11" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L11" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M11" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N11" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D12" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>154000.0</v>
+        <v>154000</v>
       </c>
       <c r="G12" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="H12" s="1">
-        <v>210160.0</v>
+        <v>210160</v>
       </c>
       <c r="I12" s="1">
-        <v>2295.0</v>
+        <v>2295</v>
       </c>
       <c r="J12" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K12" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L12" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M12" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N12" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D13" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1">
-        <v>156500.0</v>
+        <v>156500</v>
       </c>
       <c r="G13" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="H13" s="1">
-        <v>202800.0</v>
+        <v>202800</v>
       </c>
       <c r="I13" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="J13" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K13" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L13" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M13" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N13" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D14" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1">
-        <v>172500.0</v>
+        <v>172500</v>
       </c>
       <c r="G14" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="H14" s="1">
-        <v>229800.0</v>
+        <v>229800</v>
       </c>
       <c r="I14" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="J14" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K14" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L14" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M14" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N14" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D15" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1">
-        <v>180500.0</v>
+        <v>180500</v>
       </c>
       <c r="G15" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="H15" s="1">
-        <v>237800.0</v>
+        <v>237800</v>
       </c>
       <c r="I15" s="1">
-        <v>2570.0</v>
+        <v>2570</v>
       </c>
       <c r="J15" s="2">
-        <v>35080.0</v>
+        <v>35080</v>
       </c>
       <c r="K15" s="2">
-        <v>53450.0</v>
+        <v>53450</v>
       </c>
       <c r="L15" s="2">
-        <v>5850.0</v>
+        <v>5850</v>
       </c>
       <c r="M15" s="2">
-        <v>7645.0</v>
+        <v>7645</v>
       </c>
       <c r="N15" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D16" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F16" s="1">
-        <v>190800.0</v>
+        <v>190800</v>
       </c>
       <c r="G16" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="H16" s="1">
-        <v>246200.0</v>
+        <v>246200</v>
       </c>
       <c r="I16" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="J16" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K16" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L16" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M16" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N16" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D17" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1">
-        <v>206800.0</v>
+        <v>206800</v>
       </c>
       <c r="G17" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="H17" s="1">
-        <v>273200.0</v>
+        <v>273200</v>
       </c>
       <c r="I17" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="J17" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K17" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L17" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M17" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N17" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D18" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>215800.0</v>
+        <v>215800</v>
       </c>
       <c r="G18" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="H18" s="1">
-        <v>281200.0</v>
+        <v>281200</v>
       </c>
       <c r="I18" s="1">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="J18" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K18" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L18" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M18" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N18" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D19" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F19" s="1">
-        <v>205700.0</v>
+        <v>205700</v>
       </c>
       <c r="G19" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="H19" s="1">
-        <v>278000.0</v>
+        <v>278000</v>
       </c>
       <c r="I19" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="J19" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K19" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L19" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M19" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N19" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="2" t="s">
         <v>134</v>
       </c>
       <c r="D20" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1">
-        <v>217700.0</v>
+        <v>217700</v>
       </c>
       <c r="G20" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="H20" s="1">
-        <v>309000.0</v>
+        <v>309000</v>
       </c>
       <c r="I20" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="J20" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K20" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L20" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M20" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N20" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D21" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1">
-        <v>226700.0</v>
+        <v>226700</v>
       </c>
       <c r="G21" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="H21" s="1">
-        <v>318000.0</v>
+        <v>318000</v>
       </c>
       <c r="I21" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="J21" s="2">
-        <v>42490.0</v>
+        <v>42490</v>
       </c>
       <c r="K21" s="2">
-        <v>60860.0</v>
+        <v>60860</v>
       </c>
       <c r="L21" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M21" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N21" s="2">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="2" t="s">
         <v>136</v>
       </c>
@@ -4091,39 +4180,39 @@
         <v>7.5</v>
       </c>
       <c r="E22" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F22" s="1">
-        <v>220000.0</v>
+        <v>220000</v>
       </c>
       <c r="G22" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="H22" s="1">
-        <v>294800.0</v>
+        <v>294800</v>
       </c>
       <c r="I22" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="J22" s="2">
-        <v>52370.0</v>
+        <v>52370</v>
       </c>
       <c r="K22" s="2">
-        <v>70740.0</v>
+        <v>70740</v>
       </c>
       <c r="L22" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M22" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N22" s="2">
-        <v>4765.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="2" t="s">
         <v>137</v>
       </c>
@@ -4131,39 +4220,39 @@
         <v>7.5</v>
       </c>
       <c r="E23" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1">
-        <v>231000.0</v>
+        <v>231000</v>
       </c>
       <c r="G23" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="H23" s="1">
-        <v>338800.0</v>
+        <v>338800</v>
       </c>
       <c r="I23" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="J23" s="2">
-        <v>52370.0</v>
+        <v>52370</v>
       </c>
       <c r="K23" s="2">
-        <v>70740.0</v>
+        <v>70740</v>
       </c>
       <c r="L23" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M23" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N23" s="2">
-        <v>4765.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="2" t="s">
         <v>138</v>
       </c>
@@ -4171,454 +4260,455 @@
         <v>7.5</v>
       </c>
       <c r="E24" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1">
-        <v>255000.0</v>
+        <v>255000</v>
       </c>
       <c r="G24" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="H24" s="1">
-        <v>350800.0</v>
+        <v>350800</v>
       </c>
       <c r="I24" s="1">
-        <v>3890.0</v>
+        <v>3890</v>
       </c>
       <c r="J24" s="2">
-        <v>52370.0</v>
+        <v>52370</v>
       </c>
       <c r="K24" s="2">
-        <v>70740.0</v>
+        <v>70740</v>
       </c>
       <c r="L24" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M24" s="2">
-        <v>7900.0</v>
+        <v>7900</v>
       </c>
       <c r="N24" s="2">
-        <v>4765.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D25" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1">
-        <v>280300.0</v>
+        <v>280300</v>
       </c>
       <c r="G25" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="H25" s="1">
-        <v>351400.0</v>
+        <v>351400</v>
       </c>
       <c r="I25" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="J25" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K25" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L25" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M25" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N25" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D26" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1">
-        <v>306300.0</v>
+        <v>306300</v>
       </c>
       <c r="G26" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="H26" s="1">
-        <v>395400.0</v>
+        <v>395400</v>
       </c>
       <c r="I26" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="J26" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K26" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L26" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M26" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N26" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D27" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1">
-        <v>323300.0</v>
+        <v>323300</v>
       </c>
       <c r="G27" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="H27" s="1">
-        <v>412400.0</v>
+        <v>412400</v>
       </c>
       <c r="I27" s="1">
-        <v>5625.0</v>
+        <v>5625</v>
       </c>
       <c r="J27" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K27" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L27" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M27" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N27" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D28" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1">
-        <v>308000.0</v>
+        <v>308000</v>
       </c>
       <c r="G28" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="H28" s="1">
-        <v>381000.0</v>
+        <v>381000</v>
       </c>
       <c r="I28" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="J28" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K28" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L28" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M28" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N28" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D29" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F29" s="1">
-        <v>338000.0</v>
+        <v>338000</v>
       </c>
       <c r="G29" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="H29" s="1">
-        <v>431000.0</v>
+        <v>431000</v>
       </c>
       <c r="I29" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="J29" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K29" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L29" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M29" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N29" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D30" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1">
-        <v>356000.0</v>
+        <v>356000</v>
       </c>
       <c r="G30" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="H30" s="1">
-        <v>449000.0</v>
+        <v>449000</v>
       </c>
       <c r="I30" s="1">
-        <v>5900.0</v>
+        <v>5900</v>
       </c>
       <c r="J30" s="2">
-        <v>56300.0</v>
+        <v>56300</v>
       </c>
       <c r="K30" s="2">
-        <v>76570.0</v>
+        <v>76570</v>
       </c>
       <c r="L30" s="2">
-        <v>6800.0</v>
+        <v>6800</v>
       </c>
       <c r="M30" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N30" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D31" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F31" s="1">
-        <v>406000.0</v>
+        <v>406000</v>
       </c>
       <c r="G31" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="H31" s="1">
-        <v>490000.0</v>
+        <v>490000</v>
       </c>
       <c r="I31" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="J31" s="2">
-        <v>70800.0</v>
+        <v>70800</v>
       </c>
       <c r="K31" s="2">
-        <v>91070.0</v>
+        <v>91070</v>
       </c>
       <c r="L31" s="2">
-        <v>8985.0</v>
+        <v>8985</v>
       </c>
       <c r="M31" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N31" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D32" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1">
-        <v>439000.0</v>
+        <v>439000</v>
       </c>
       <c r="G32" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="H32" s="1">
-        <v>542000.0</v>
+        <v>542000</v>
       </c>
       <c r="I32" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="J32" s="2">
-        <v>70800.0</v>
+        <v>70800</v>
       </c>
       <c r="K32" s="2">
-        <v>91070.0</v>
+        <v>91070</v>
       </c>
       <c r="L32" s="2">
-        <v>8985.0</v>
+        <v>8985</v>
       </c>
       <c r="M32" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N32" s="2">
-        <v>5485.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
       <c r="C33" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D33" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1">
-        <v>459000.0</v>
+        <v>459000</v>
       </c>
       <c r="G33" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="H33" s="1">
-        <v>562000.0</v>
+        <v>562000</v>
       </c>
       <c r="I33" s="1">
-        <v>6665.0</v>
+        <v>6665</v>
       </c>
       <c r="J33" s="2">
-        <v>70800.0</v>
+        <v>70800</v>
       </c>
       <c r="K33" s="2">
-        <v>91070.0</v>
+        <v>91070</v>
       </c>
       <c r="L33" s="2">
-        <v>8985.0</v>
+        <v>8985</v>
       </c>
       <c r="M33" s="2">
-        <v>8350.0</v>
+        <v>8350</v>
       </c>
       <c r="N33" s="2">
-        <v>5485.0</v>
+        <v>5485</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A3:A33"/>
+    <mergeCell ref="B3:B33"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="F1:N1"/>
-    <mergeCell ref="A3:A33"/>
-    <mergeCell ref="B3:B33"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.5"/>
-    <col customWidth="1" min="2" max="2" width="14.25"/>
-    <col customWidth="1" min="3" max="3" width="6.5"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="13.5"/>
-    <col customWidth="1" min="6" max="6" width="12.88"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="1" t="s">
         <v>149</v>
       </c>
@@ -4626,8 +4716,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
         <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4637,20 +4727,20 @@
         <v>153</v>
       </c>
       <c r="D3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="1">
-        <v>60600.0</v>
+        <v>60600</v>
       </c>
       <c r="G3" s="1">
-        <v>56330.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
+        <v>56330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>152</v>
       </c>
@@ -4658,20 +4748,20 @@
         <v>154</v>
       </c>
       <c r="D4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F4" s="1">
-        <v>91550.0</v>
+        <v>91550</v>
       </c>
       <c r="G4" s="1">
-        <v>87280.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
+        <v>87280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
@@ -4679,20 +4769,20 @@
         <v>155</v>
       </c>
       <c r="D5" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="F5" s="1">
-        <v>67075.0</v>
+        <v>67075</v>
       </c>
       <c r="G5" s="1">
-        <v>63235.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
+        <v>63235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
       <c r="B6" s="1" t="s">
         <v>152</v>
       </c>
@@ -4700,20 +4790,20 @@
         <v>156</v>
       </c>
       <c r="D6" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>99635.0</v>
+        <v>99635</v>
       </c>
       <c r="G6" s="1">
-        <v>95800.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
+        <v>95800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>152</v>
       </c>
@@ -4721,20 +4811,20 @@
         <v>157</v>
       </c>
       <c r="D7" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="F7" s="1">
-        <v>77090.0</v>
+        <v>77090</v>
       </c>
       <c r="G7" s="1">
-        <v>83355.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
+        <v>83355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>152</v>
       </c>
@@ -4742,20 +4832,20 @@
         <v>158</v>
       </c>
       <c r="D8" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F8" s="1">
-        <v>123490.0</v>
+        <v>123490</v>
       </c>
       <c r="G8" s="1">
-        <v>129870.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
+        <v>129870</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
       <c r="B9" s="1" t="s">
         <v>152</v>
       </c>
@@ -4763,20 +4853,20 @@
         <v>159</v>
       </c>
       <c r="D9" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F9" s="1">
-        <v>168825.0</v>
+        <v>168825</v>
       </c>
       <c r="G9" s="1">
-        <v>182735.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
+        <v>182735</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>160</v>
       </c>
@@ -4784,20 +4874,20 @@
         <v>161</v>
       </c>
       <c r="D10" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F10" s="1">
-        <v>115325.0</v>
+        <v>115325</v>
       </c>
       <c r="G10" s="1">
-        <v>110365.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
+        <v>110365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>160</v>
       </c>
@@ -4805,20 +4895,20 @@
         <v>162</v>
       </c>
       <c r="D11" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F11" s="1">
-        <v>121650.0</v>
+        <v>121650</v>
       </c>
       <c r="G11" s="1">
-        <v>138265.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
+        <v>138265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10"/>
       <c r="B12" s="1" t="s">
         <v>160</v>
       </c>
@@ -4826,20 +4916,20 @@
         <v>163</v>
       </c>
       <c r="D12" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F12" s="1">
-        <v>157720.0</v>
+        <v>157720</v>
       </c>
       <c r="G12" s="1">
-        <v>164165.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
+        <v>164165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>160</v>
       </c>
@@ -4847,20 +4937,20 @@
         <v>164</v>
       </c>
       <c r="D13" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F13" s="1">
-        <v>218075.0</v>
+        <v>218075</v>
       </c>
       <c r="G13" s="1">
-        <v>227000.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
+        <v>227000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
@@ -4871,17 +4961,17 @@
         <v>7.5</v>
       </c>
       <c r="E14" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="1">
-        <v>283035.0</v>
+        <v>283035</v>
       </c>
       <c r="G14" s="1">
-        <v>299175.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5"/>
+        <v>299175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>160</v>
       </c>
@@ -4889,245 +4979,246 @@
         <v>166</v>
       </c>
       <c r="D15" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="F15" s="1">
-        <v>301090.0</v>
+        <v>301090</v>
       </c>
       <c r="G15" s="1">
-        <v>407545.0</v>
+        <v>407545</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A3:A15"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A3:A15"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="2" width="14.75"/>
-    <col customWidth="1" min="3" max="3" width="5.88"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="14.13"/>
-    <col customWidth="1" min="6" max="6" width="10.25"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="7">
-        <v>1.0</v>
+      <c r="D2" s="4">
+        <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="F2" s="1">
-        <v>11060.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>11060</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="7">
-        <v>1.0</v>
+      <c r="D3" s="4">
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>4700.0</v>
+        <v>4700</v>
       </c>
       <c r="F3" s="1">
-        <v>17205.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>17205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="7">
-        <v>1.0</v>
+      <c r="D4" s="4">
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>5500.0</v>
+        <v>5500</v>
       </c>
       <c r="F4" s="1">
-        <v>17900.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="7">
-        <v>2.0</v>
+      <c r="D5" s="4">
+        <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>2850.0</v>
+        <v>2850</v>
       </c>
       <c r="F5" s="1">
-        <v>14335.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+        <v>14335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="7">
-        <v>2.0</v>
+      <c r="D6" s="4">
+        <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>4750.0</v>
+        <v>4750</v>
       </c>
       <c r="F6" s="1">
-        <v>21835.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+        <v>21835</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="7">
-        <v>2.0</v>
+      <c r="D7" s="4">
+        <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>5550.0</v>
+        <v>5550</v>
       </c>
       <c r="F7" s="1">
-        <v>22855.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+        <v>22855</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="7">
-        <v>3.0</v>
+      <c r="D8" s="4">
+        <v>3</v>
       </c>
       <c r="E8" s="1">
-        <v>2850.0</v>
+        <v>2850</v>
       </c>
       <c r="F8" s="1">
-        <v>19640.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+        <v>19640</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="7">
-        <v>3.0</v>
+      <c r="D9" s="4">
+        <v>3</v>
       </c>
       <c r="E9" s="1">
-        <v>4750.0</v>
+        <v>4750</v>
       </c>
       <c r="F9" s="1">
-        <v>29075.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+        <v>29075</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="7">
-        <v>3.0</v>
+      <c r="D10" s="4">
+        <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>5550.0</v>
+        <v>5550</v>
       </c>
       <c r="F10" s="1">
-        <v>30545.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+        <v>30545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="7">
-        <v>5.0</v>
+      <c r="D11" s="4">
+        <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>4800.0</v>
+        <v>4800</v>
       </c>
       <c r="F11" s="1">
-        <v>41655.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+        <v>41655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D12" s="7">
-        <v>5.0</v>
+      <c r="D12" s="4">
+        <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>5600.0</v>
+        <v>5600</v>
       </c>
       <c r="F12" s="1">
-        <v>44025.0</v>
+        <v>44025</v>
       </c>
     </row>
   </sheetData>
@@ -5135,133 +5226,120 @@
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="B2:B12"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0000FF"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.88"/>
-    <col customWidth="1" min="2" max="2" width="9.5"/>
-    <col customWidth="1" min="3" max="3" width="7.38"/>
-    <col customWidth="1" min="4" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="22.25"/>
-    <col customWidth="1" min="6" max="6" width="10.25"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>183</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="17">
         <v>1.5</v>
       </c>
       <c r="E2" s="17">
-        <v>550.0</v>
+        <v>550</v>
       </c>
       <c r="F2" s="17">
-        <v>16000.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <v>1.5</v>
       </c>
       <c r="E3" s="17">
-        <v>685.0</v>
+        <v>685</v>
       </c>
       <c r="F3" s="17">
-        <v>16500.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <v>2.5</v>
       </c>
       <c r="E4" s="17">
-        <v>550.0</v>
+        <v>550</v>
       </c>
       <c r="F4" s="17">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>2.5</v>
       </c>
       <c r="E5" s="17">
-        <v>685.0</v>
+        <v>685</v>
       </c>
       <c r="F5" s="17">
-        <v>17500.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="17">
-        <v>4.0</v>
-      </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="17">
-        <v>42000.0</v>
+        <v>14600</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>